--- a/data/trans_dic/P32E$eventos_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32E$eventos_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos</t>
+          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,28</t>
+          <t>0,0; 35,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,88</t>
+          <t>0,0; 35,46</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,54</t>
+          <t>0,0; 19,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,67</t>
+          <t>0,0; 49,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 24,67</t>
+          <t>2,56; 23,68</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,7</t>
+          <t>0,0; 40,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,28</t>
+          <t>0,0; 10,72</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,46</t>
+          <t>0,58; 5,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,99; 21,94</t>
+          <t>2,17; 22,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,78</t>
+          <t>1,63; 8,08</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos</t>
+          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1256</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 985</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1289</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2368</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1073</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2262</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5442</t>
+          <t>0; 5365</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>226; 987</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5736</t>
+          <t>0; 5669</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2062</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1496</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1842</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1135</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 310</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 948</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1689</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1320</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1647</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 7098</t>
+          <t>0; 6489</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 7900</t>
+          <t>0; 7574</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1136; 11901</t>
+          <t>1236; 11425</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 6168</t>
+          <t>0; 6520</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 6552</t>
+          <t>0; 6223</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>897; 9310</t>
+          <t>831; 8005</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1634; 12007</t>
+          <t>1189; 12378</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3600; 15474</t>
+          <t>3232; 16067</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$eventos_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32E$eventos_2023-Provincia-trans_dic.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,77</t>
+          <t>0,0; 31,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,46</t>
+          <t>0,0; 33,75</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,69</t>
+          <t>0,0; 14,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,53</t>
+          <t>0,0; 40,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 23,68</t>
+          <t>1,8; 18,44</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,91</t>
+          <t>0,0; 36,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,72</t>
+          <t>0,0; 11,07</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,56</t>
+          <t>0,55; 4,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,17; 22,62</t>
+          <t>2,55; 19,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 8,08</t>
+          <t>1,71; 7,26</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>924</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1868</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5365</t>
+          <t>0; 5140</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5669</t>
+          <t>0; 5798</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>4936</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 6489</t>
+          <t>0; 6548</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 7574</t>
+          <t>0; 7871</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1236; 11425</t>
+          <t>1144; 11721</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1353</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 6520</t>
+          <t>0; 6774</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 6223</t>
+          <t>0; 7218</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8157</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>831; 8005</t>
+          <t>880; 7733</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1189; 12378</t>
+          <t>1638; 12261</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3232; 16067</t>
+          <t>3861; 16381</t>
         </is>
       </c>
     </row>
